--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Matrimoni, unioni civili e convivenze di fatto.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Matrimoni, unioni civili e convivenze di fatto.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="175">
   <si>
     <r>
       <t xml:space="preserve">
@@ -782,7 +782,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 Puoi </t>
     </r>
     <r>
@@ -1416,7 +1416,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 Per procedere con la celebrazione, dovete confermare la data.</t>
     </r>
   </si>
@@ -1486,7 +1486,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1593,17 +1593,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi dell'appuntamento tramite notifica push.</t>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
   <si>
     <t>…voglio ricevere conferma dei miei appuntamenti</t>
@@ -1738,7 +1727,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">Ti confermiamo che  </t>
+      <t xml:space="preserve">Ti confermiamo che </t>
     </r>
     <r>
       <rPr>
@@ -3290,7 +3279,7 @@
         <v>145</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="C11" s="35" t="s">
         <v>73</v>
@@ -3302,16 +3291,16 @@
         <v>73</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>73</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="I11" s="35" t="s">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="J11" s="35" t="s">
         <v>73</v>
@@ -3326,7 +3315,7 @@
         <v>73</v>
       </c>
       <c r="N11" s="35" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="O11" s="35" t="s">
         <v>73</v>
@@ -32802,7 +32791,7 @@
         <v>76</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>76</v>
@@ -32811,7 +32800,7 @@
         <v>76</v>
       </c>
       <c r="I2" s="35" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -32860,13 +32849,13 @@
         <v>88</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G4" s="34" t="s">
         <v>89</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I4" s="34" t="s">
         <v>96</v>
@@ -32880,25 +32869,25 @@
         <v>98</v>
       </c>
       <c r="C5" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="F5" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="G5" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="H5" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="I5" s="35" t="s">
         <v>156</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="H5" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="I5" s="35" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -32993,28 +32982,28 @@
         <v>121</v>
       </c>
       <c r="B9" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="F9" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="G9" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="E9" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>165</v>
-      </c>
       <c r="H9" s="35" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I9" s="35" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -33025,13 +33014,13 @@
         <v>131</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D10" s="35" t="s">
         <v>132</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F10" s="35" t="s">
         <v>142</v>
@@ -33040,10 +33029,10 @@
         <v>134</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I10" s="35" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -33051,10 +33040,10 @@
         <v>145</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="D11" s="35" t="s">
         <v>73</v>
@@ -33109,7 +33098,7 @@
         <v>76</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -33131,7 +33120,7 @@
         <v>88</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -33139,10 +33128,10 @@
         <v>97</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -33183,10 +33172,10 @@
         <v>121</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -33194,10 +33183,10 @@
         <v>130</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
